--- a/results/excel/result4_v2.xlsx
+++ b/results/excel/result4_v2.xlsx
@@ -466,69 +466,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C2" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D2" t="n">
-        <v>1523</v>
+        <v>306</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>6455</v>
+        <v>6379</v>
       </c>
       <c r="G2" t="n">
-        <v>1211</v>
+        <v>1010</v>
       </c>
       <c r="H2" t="n">
-        <v>6031</v>
+        <v>5030</v>
       </c>
       <c r="I2" t="n">
-        <v>245</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C3" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D3" t="n">
-        <v>1277</v>
+        <v>909</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2954</v>
+        <v>6379</v>
       </c>
       <c r="G3" t="n">
-        <v>792</v>
+        <v>1010</v>
       </c>
       <c r="H3" t="n">
-        <v>3900</v>
+        <v>5030</v>
       </c>
       <c r="I3" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -538,7 +538,7 @@
         <v>8878077181</v>
       </c>
       <c r="D4" t="n">
-        <v>5778</v>
+        <v>1048</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
@@ -547,13 +547,13 @@
         <v>1177</v>
       </c>
       <c r="G4" t="n">
-        <v>1198</v>
+        <v>1173</v>
       </c>
       <c r="H4" t="n">
-        <v>6026</v>
+        <v>5774</v>
       </c>
       <c r="I4" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
@@ -563,65 +563,65 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C5" t="n">
-        <v>8878077181</v>
+        <v>2526158329</v>
       </c>
       <c r="D5" t="n">
-        <v>3989</v>
+        <v>1277</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1177</v>
+        <v>3408</v>
       </c>
       <c r="G5" t="n">
-        <v>1198</v>
+        <v>912</v>
       </c>
       <c r="H5" t="n">
-        <v>6026</v>
+        <v>4528</v>
       </c>
       <c r="I5" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C6" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D6" t="n">
-        <v>3989</v>
+        <v>711</v>
       </c>
       <c r="E6" t="n">
         <v>610.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1177</v>
+        <v>6379</v>
       </c>
       <c r="G6" t="n">
-        <v>1198</v>
+        <v>1010</v>
       </c>
       <c r="H6" t="n">
-        <v>6026</v>
+        <v>5030</v>
       </c>
       <c r="I6" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,7 +631,7 @@
         <v>9628223555</v>
       </c>
       <c r="D7" t="n">
-        <v>1764</v>
+        <v>1094</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
@@ -640,13 +640,13 @@
         <v>6379</v>
       </c>
       <c r="G7" t="n">
-        <v>988</v>
+        <v>1010</v>
       </c>
       <c r="H7" t="n">
-        <v>4811</v>
+        <v>5030</v>
       </c>
       <c r="I7" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
@@ -656,65 +656,65 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C8" t="n">
-        <v>8878077181</v>
+        <v>2526158329</v>
       </c>
       <c r="D8" t="n">
-        <v>3989</v>
+        <v>3791</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1177</v>
+        <v>3408</v>
       </c>
       <c r="G8" t="n">
-        <v>1198</v>
+        <v>912</v>
       </c>
       <c r="H8" t="n">
-        <v>6026</v>
+        <v>4528</v>
       </c>
       <c r="I8" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C9" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D9" t="n">
-        <v>2186</v>
+        <v>4718</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G9" t="n">
-        <v>988</v>
+        <v>1214</v>
       </c>
       <c r="H9" t="n">
-        <v>4811</v>
+        <v>6063</v>
       </c>
       <c r="I9" t="n">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -724,7 +724,7 @@
         <v>9630806627</v>
       </c>
       <c r="D10" t="n">
-        <v>4419</v>
+        <v>2587</v>
       </c>
       <c r="E10" t="n">
         <v>610.08</v>
@@ -733,50 +733,50 @@
         <v>6966</v>
       </c>
       <c r="G10" t="n">
-        <v>1004</v>
+        <v>914</v>
       </c>
       <c r="H10" t="n">
-        <v>5044</v>
+        <v>4187</v>
       </c>
       <c r="I10" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C11" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D11" t="n">
-        <v>3989</v>
+        <v>5699</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1177</v>
+        <v>8141</v>
       </c>
       <c r="G11" t="n">
-        <v>1198</v>
+        <v>799</v>
       </c>
       <c r="H11" t="n">
-        <v>6026</v>
+        <v>4018</v>
       </c>
       <c r="I11" t="n">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -786,7 +786,7 @@
         <v>4190988309</v>
       </c>
       <c r="D12" t="n">
-        <v>5900</v>
+        <v>5268</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
@@ -795,10 +795,10 @@
         <v>8141</v>
       </c>
       <c r="G12" t="n">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="H12" t="n">
-        <v>4035</v>
+        <v>4018</v>
       </c>
       <c r="I12" t="n">
         <v>153</v>
@@ -807,79 +807,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C13" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D13" t="n">
-        <v>1608</v>
+        <v>5637</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>6966</v>
+        <v>6455</v>
       </c>
       <c r="G13" t="n">
-        <v>1004</v>
+        <v>1214</v>
       </c>
       <c r="H13" t="n">
-        <v>5044</v>
+        <v>6063</v>
       </c>
       <c r="I13" t="n">
-        <v>195</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C14" t="n">
-        <v>1841014603</v>
+        <v>9630806627</v>
       </c>
       <c r="D14" t="n">
-        <v>4713</v>
+        <v>1656</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>2954</v>
+        <v>6966</v>
       </c>
       <c r="G14" t="n">
-        <v>792</v>
+        <v>914</v>
       </c>
       <c r="H14" t="n">
-        <v>3900</v>
+        <v>4187</v>
       </c>
       <c r="I14" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C15" t="n">
         <v>9630806627</v>
       </c>
       <c r="D15" t="n">
-        <v>216</v>
+        <v>6133</v>
       </c>
       <c r="E15" t="n">
         <v>610.08</v>
@@ -888,168 +888,168 @@
         <v>6966</v>
       </c>
       <c r="G15" t="n">
-        <v>1004</v>
+        <v>914</v>
       </c>
       <c r="H15" t="n">
-        <v>5044</v>
+        <v>4187</v>
       </c>
       <c r="I15" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C16" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D16" t="n">
-        <v>5374</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
       </c>
       <c r="F16" t="n">
-        <v>8141</v>
+        <v>6455</v>
       </c>
       <c r="G16" t="n">
-        <v>801</v>
+        <v>1214</v>
       </c>
       <c r="H16" t="n">
-        <v>4035</v>
+        <v>6063</v>
       </c>
       <c r="I16" t="n">
-        <v>153</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>63563817</v>
       </c>
       <c r="C17" t="n">
-        <v>4190988309</v>
+        <v>2526158329</v>
       </c>
       <c r="D17" t="n">
-        <v>886</v>
+        <v>6604</v>
       </c>
       <c r="E17" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F17" t="n">
-        <v>8141</v>
+        <v>1704</v>
       </c>
       <c r="G17" t="n">
-        <v>801</v>
+        <v>456</v>
       </c>
       <c r="H17" t="n">
-        <v>4035</v>
+        <v>2263</v>
       </c>
       <c r="I17" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>495403620</v>
       </c>
       <c r="C18" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D18" t="n">
-        <v>6294</v>
+        <v>5778</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
       </c>
       <c r="F18" t="n">
-        <v>6379</v>
+        <v>1177</v>
       </c>
       <c r="G18" t="n">
-        <v>988</v>
+        <v>1173</v>
       </c>
       <c r="H18" t="n">
-        <v>4811</v>
+        <v>5774</v>
       </c>
       <c r="I18" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C19" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D19" t="n">
-        <v>2518</v>
+        <v>6207</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>6455</v>
+        <v>8141</v>
       </c>
       <c r="G19" t="n">
-        <v>1211</v>
+        <v>799</v>
       </c>
       <c r="H19" t="n">
-        <v>6031</v>
+        <v>4018</v>
       </c>
       <c r="I19" t="n">
-        <v>245</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C20" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D20" t="n">
-        <v>3303</v>
+        <v>1607</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>6966</v>
+        <v>1177</v>
       </c>
       <c r="G20" t="n">
-        <v>1004</v>
+        <v>1173</v>
       </c>
       <c r="H20" t="n">
-        <v>5044</v>
+        <v>5774</v>
       </c>
       <c r="I20" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
@@ -1065,7 +1065,7 @@
         <v>4190988309</v>
       </c>
       <c r="D21" t="n">
-        <v>6602</v>
+        <v>2977</v>
       </c>
       <c r="E21" t="n">
         <v>610.08</v>
@@ -1074,10 +1074,10 @@
         <v>8141</v>
       </c>
       <c r="G21" t="n">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="H21" t="n">
-        <v>4035</v>
+        <v>4018</v>
       </c>
       <c r="I21" t="n">
         <v>153</v>
@@ -1086,32 +1086,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C22" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D22" t="n">
-        <v>2725</v>
+        <v>3070</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>8141</v>
+        <v>6379</v>
       </c>
       <c r="G22" t="n">
-        <v>801</v>
+        <v>1010</v>
       </c>
       <c r="H22" t="n">
-        <v>4035</v>
+        <v>5030</v>
       </c>
       <c r="I22" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23">
@@ -1127,7 +1127,7 @@
         <v>9811363528</v>
       </c>
       <c r="D23" t="n">
-        <v>4583</v>
+        <v>1296</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
@@ -1136,137 +1136,137 @@
         <v>6455</v>
       </c>
       <c r="G23" t="n">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="H23" t="n">
-        <v>6031</v>
+        <v>6063</v>
       </c>
       <c r="I23" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C24" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D24" t="n">
-        <v>1048</v>
+        <v>152</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
       </c>
       <c r="F24" t="n">
-        <v>1177</v>
+        <v>8141</v>
       </c>
       <c r="G24" t="n">
-        <v>1198</v>
+        <v>799</v>
       </c>
       <c r="H24" t="n">
-        <v>6026</v>
+        <v>4018</v>
       </c>
       <c r="I24" t="n">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C25" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D25" t="n">
-        <v>4579</v>
+        <v>4171</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
       </c>
       <c r="F25" t="n">
-        <v>6966</v>
+        <v>6379</v>
       </c>
       <c r="G25" t="n">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="H25" t="n">
-        <v>5044</v>
+        <v>5030</v>
       </c>
       <c r="I25" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C26" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D26" t="n">
-        <v>6082</v>
+        <v>3575</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
       </c>
       <c r="F26" t="n">
-        <v>8141</v>
+        <v>6455</v>
       </c>
       <c r="G26" t="n">
-        <v>801</v>
+        <v>1214</v>
       </c>
       <c r="H26" t="n">
-        <v>4035</v>
+        <v>6063</v>
       </c>
       <c r="I26" t="n">
-        <v>153</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C27" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D27" t="n">
-        <v>5699</v>
+        <v>3989</v>
       </c>
       <c r="E27" t="n">
         <v>610.08</v>
       </c>
       <c r="F27" t="n">
-        <v>8141</v>
+        <v>1177</v>
       </c>
       <c r="G27" t="n">
-        <v>801</v>
+        <v>1173</v>
       </c>
       <c r="H27" t="n">
-        <v>4035</v>
+        <v>5774</v>
       </c>
       <c r="I27" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28">
@@ -1276,127 +1276,127 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C28" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D28" t="n">
-        <v>4323</v>
+        <v>5699</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>6455</v>
+        <v>8141</v>
       </c>
       <c r="G28" t="n">
-        <v>1211</v>
+        <v>799</v>
       </c>
       <c r="H28" t="n">
-        <v>6031</v>
+        <v>4018</v>
       </c>
       <c r="I28" t="n">
-        <v>245</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C29" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D29" t="n">
-        <v>671</v>
+        <v>6514</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>6455</v>
+        <v>6966</v>
       </c>
       <c r="G29" t="n">
-        <v>1211</v>
+        <v>914</v>
       </c>
       <c r="H29" t="n">
-        <v>6031</v>
+        <v>4187</v>
       </c>
       <c r="I29" t="n">
-        <v>245</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C30" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D30" t="n">
-        <v>3989</v>
+        <v>1098</v>
       </c>
       <c r="E30" t="n">
         <v>610.08</v>
       </c>
       <c r="F30" t="n">
-        <v>1177</v>
+        <v>8141</v>
       </c>
       <c r="G30" t="n">
-        <v>1198</v>
+        <v>799</v>
       </c>
       <c r="H30" t="n">
-        <v>6026</v>
+        <v>4018</v>
       </c>
       <c r="I30" t="n">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C31" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D31" t="n">
-        <v>6489</v>
+        <v>1607</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
       </c>
       <c r="F31" t="n">
-        <v>6966</v>
+        <v>1177</v>
       </c>
       <c r="G31" t="n">
-        <v>1004</v>
+        <v>1173</v>
       </c>
       <c r="H31" t="n">
-        <v>5044</v>
+        <v>5774</v>
       </c>
       <c r="I31" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1406,7 +1406,7 @@
         <v>9628223555</v>
       </c>
       <c r="D32" t="n">
-        <v>3481</v>
+        <v>609</v>
       </c>
       <c r="E32" t="n">
         <v>610.08</v>
@@ -1415,44 +1415,44 @@
         <v>6379</v>
       </c>
       <c r="G32" t="n">
-        <v>988</v>
+        <v>1010</v>
       </c>
       <c r="H32" t="n">
-        <v>4811</v>
+        <v>5030</v>
       </c>
       <c r="I32" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C33" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D33" t="n">
-        <v>5436</v>
+        <v>4593</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>6379</v>
+        <v>6966</v>
       </c>
       <c r="G33" t="n">
-        <v>988</v>
+        <v>914</v>
       </c>
       <c r="H33" t="n">
-        <v>4811</v>
+        <v>4187</v>
       </c>
       <c r="I33" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C34" t="n">
-        <v>9630806627</v>
+        <v>2526158329</v>
       </c>
       <c r="D34" t="n">
-        <v>3135</v>
+        <v>2397</v>
       </c>
       <c r="E34" t="n">
         <v>610.08</v>
       </c>
       <c r="F34" t="n">
-        <v>6966</v>
+        <v>3408</v>
       </c>
       <c r="G34" t="n">
-        <v>1004</v>
+        <v>912</v>
       </c>
       <c r="H34" t="n">
-        <v>5044</v>
+        <v>4528</v>
       </c>
       <c r="I34" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C35" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D35" t="n">
-        <v>5035</v>
+        <v>5219</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G35" t="n">
-        <v>988</v>
+        <v>1214</v>
       </c>
       <c r="H35" t="n">
-        <v>4811</v>
+        <v>6063</v>
       </c>
       <c r="I35" t="n">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
@@ -1527,149 +1527,149 @@
         <v>525368335</v>
       </c>
       <c r="C36" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D36" t="n">
-        <v>2843</v>
+        <v>1402</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G36" t="n">
-        <v>988</v>
+        <v>1214</v>
       </c>
       <c r="H36" t="n">
-        <v>4811</v>
+        <v>6063</v>
       </c>
       <c r="I36" t="n">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>525368335</v>
       </c>
       <c r="C37" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D37" t="n">
-        <v>62</v>
+        <v>3989</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
       </c>
       <c r="F37" t="n">
-        <v>6455</v>
+        <v>1177</v>
       </c>
       <c r="G37" t="n">
-        <v>1211</v>
+        <v>1173</v>
       </c>
       <c r="H37" t="n">
-        <v>6031</v>
+        <v>5774</v>
       </c>
       <c r="I37" t="n">
-        <v>245</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C38" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D38" t="n">
-        <v>4048</v>
+        <v>1048</v>
       </c>
       <c r="E38" t="n">
         <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>2954</v>
+        <v>1177</v>
       </c>
       <c r="G38" t="n">
-        <v>792</v>
+        <v>1173</v>
       </c>
       <c r="H38" t="n">
-        <v>3900</v>
+        <v>5774</v>
       </c>
       <c r="I38" t="n">
-        <v>133</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C39" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D39" t="n">
-        <v>1496</v>
+        <v>815</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6455</v>
+        <v>6966</v>
       </c>
       <c r="G39" t="n">
-        <v>1211</v>
+        <v>914</v>
       </c>
       <c r="H39" t="n">
-        <v>6031</v>
+        <v>4187</v>
       </c>
       <c r="I39" t="n">
-        <v>245</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C40" t="n">
-        <v>1841014603</v>
+        <v>9630806627</v>
       </c>
       <c r="D40" t="n">
-        <v>4773</v>
+        <v>2195</v>
       </c>
       <c r="E40" t="n">
-        <v>305.04</v>
+        <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>1477</v>
+        <v>6966</v>
       </c>
       <c r="G40" t="n">
-        <v>396</v>
+        <v>914</v>
       </c>
       <c r="H40" t="n">
-        <v>1950</v>
+        <v>4187</v>
       </c>
       <c r="I40" t="n">
-        <v>66</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result4_v2.xlsx
+++ b/results/excel/result4_v2.xlsx
@@ -466,156 +466,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C2" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D2" t="n">
-        <v>306</v>
+        <v>3202</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G2" t="n">
-        <v>1010</v>
+        <v>1197</v>
       </c>
       <c r="H2" t="n">
-        <v>5030</v>
+        <v>5892</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C3" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D3" t="n">
-        <v>909</v>
+        <v>4340</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G3" t="n">
-        <v>1010</v>
+        <v>1197</v>
       </c>
       <c r="H3" t="n">
-        <v>5030</v>
+        <v>5892</v>
       </c>
       <c r="I3" t="n">
-        <v>165</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C4" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D4" t="n">
-        <v>1048</v>
+        <v>4870</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1177</v>
+        <v>6966</v>
       </c>
       <c r="G4" t="n">
-        <v>1173</v>
+        <v>961</v>
       </c>
       <c r="H4" t="n">
-        <v>5774</v>
+        <v>4624</v>
       </c>
       <c r="I4" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>63563817</v>
       </c>
       <c r="C5" t="n">
-        <v>2526158329</v>
+        <v>4190988309</v>
       </c>
       <c r="D5" t="n">
-        <v>1277</v>
+        <v>6083</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>3408</v>
+        <v>8141</v>
       </c>
       <c r="G5" t="n">
-        <v>912</v>
+        <v>798</v>
       </c>
       <c r="H5" t="n">
-        <v>4528</v>
+        <v>4000</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>495403620</v>
       </c>
       <c r="C6" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D6" t="n">
-        <v>711</v>
+        <v>1048</v>
       </c>
       <c r="E6" t="n">
         <v>610.08</v>
       </c>
       <c r="F6" t="n">
-        <v>6379</v>
+        <v>1177</v>
       </c>
       <c r="G6" t="n">
-        <v>1010</v>
+        <v>1150</v>
       </c>
       <c r="H6" t="n">
-        <v>5030</v>
+        <v>5546</v>
       </c>
       <c r="I6" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -628,118 +628,118 @@
         <v>495403620</v>
       </c>
       <c r="C7" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D7" t="n">
-        <v>1094</v>
+        <v>1607</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
       </c>
       <c r="F7" t="n">
-        <v>6379</v>
+        <v>1177</v>
       </c>
       <c r="G7" t="n">
-        <v>1010</v>
+        <v>1150</v>
       </c>
       <c r="H7" t="n">
-        <v>5030</v>
+        <v>5546</v>
       </c>
       <c r="I7" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C8" t="n">
-        <v>2526158329</v>
+        <v>9811363528</v>
       </c>
       <c r="D8" t="n">
-        <v>3791</v>
+        <v>2742</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>3408</v>
+        <v>6455</v>
       </c>
       <c r="G8" t="n">
-        <v>912</v>
+        <v>1197</v>
       </c>
       <c r="H8" t="n">
-        <v>4528</v>
+        <v>5892</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C9" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D9" t="n">
-        <v>4718</v>
+        <v>4101</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>6455</v>
+        <v>8141</v>
       </c>
       <c r="G9" t="n">
-        <v>1214</v>
+        <v>798</v>
       </c>
       <c r="H9" t="n">
-        <v>6063</v>
+        <v>4000</v>
       </c>
       <c r="I9" t="n">
-        <v>246</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C10" t="n">
-        <v>9630806627</v>
+        <v>2526158329</v>
       </c>
       <c r="D10" t="n">
-        <v>2587</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F10" t="n">
-        <v>6966</v>
+        <v>1704</v>
       </c>
       <c r="G10" t="n">
-        <v>914</v>
+        <v>459</v>
       </c>
       <c r="H10" t="n">
-        <v>4187</v>
+        <v>2294</v>
       </c>
       <c r="I10" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>4190988309</v>
       </c>
       <c r="D11" t="n">
-        <v>5699</v>
+        <v>4017</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
@@ -764,10 +764,10 @@
         <v>8141</v>
       </c>
       <c r="G11" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H11" t="n">
-        <v>4018</v>
+        <v>4000</v>
       </c>
       <c r="I11" t="n">
         <v>153</v>
@@ -776,32 +776,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C12" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D12" t="n">
-        <v>5268</v>
+        <v>4931</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
       </c>
       <c r="F12" t="n">
-        <v>8141</v>
+        <v>6379</v>
       </c>
       <c r="G12" t="n">
-        <v>799</v>
+        <v>934</v>
       </c>
       <c r="H12" t="n">
-        <v>4018</v>
+        <v>4305</v>
       </c>
       <c r="I12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -811,96 +811,96 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C13" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D13" t="n">
-        <v>5637</v>
+        <v>1607</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>6455</v>
+        <v>1177</v>
       </c>
       <c r="G13" t="n">
-        <v>1214</v>
+        <v>1150</v>
       </c>
       <c r="H13" t="n">
-        <v>6063</v>
+        <v>5546</v>
       </c>
       <c r="I13" t="n">
-        <v>246</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C14" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D14" t="n">
-        <v>1656</v>
+        <v>2795</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>6966</v>
+        <v>6379</v>
       </c>
       <c r="G14" t="n">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="H14" t="n">
-        <v>4187</v>
+        <v>4305</v>
       </c>
       <c r="I14" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C15" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D15" t="n">
-        <v>6133</v>
+        <v>3060</v>
       </c>
       <c r="E15" t="n">
         <v>610.08</v>
       </c>
       <c r="F15" t="n">
-        <v>6966</v>
+        <v>6379</v>
       </c>
       <c r="G15" t="n">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="H15" t="n">
-        <v>4187</v>
+        <v>4305</v>
       </c>
       <c r="I15" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -910,7 +910,7 @@
         <v>9811363528</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>2233</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
@@ -919,143 +919,143 @@
         <v>6455</v>
       </c>
       <c r="G16" t="n">
-        <v>1214</v>
+        <v>1197</v>
       </c>
       <c r="H16" t="n">
-        <v>6063</v>
+        <v>5892</v>
       </c>
       <c r="I16" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C17" t="n">
-        <v>2526158329</v>
+        <v>9811363528</v>
       </c>
       <c r="D17" t="n">
-        <v>6604</v>
+        <v>5497</v>
       </c>
       <c r="E17" t="n">
-        <v>304.94</v>
+        <v>610.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1704</v>
+        <v>6455</v>
       </c>
       <c r="G17" t="n">
-        <v>456</v>
+        <v>1197</v>
       </c>
       <c r="H17" t="n">
-        <v>2263</v>
+        <v>5892</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>495403620</v>
       </c>
       <c r="C18" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D18" t="n">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
       </c>
       <c r="F18" t="n">
-        <v>1177</v>
+        <v>6379</v>
       </c>
       <c r="G18" t="n">
-        <v>1173</v>
+        <v>934</v>
       </c>
       <c r="H18" t="n">
-        <v>5774</v>
+        <v>4305</v>
       </c>
       <c r="I18" t="n">
-        <v>199</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C19" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D19" t="n">
-        <v>6207</v>
+        <v>2859</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>8141</v>
+        <v>6455</v>
       </c>
       <c r="G19" t="n">
-        <v>799</v>
+        <v>1197</v>
       </c>
       <c r="H19" t="n">
-        <v>4018</v>
+        <v>5892</v>
       </c>
       <c r="I19" t="n">
-        <v>153</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C20" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D20" t="n">
-        <v>1607</v>
+        <v>6256</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1177</v>
+        <v>6966</v>
       </c>
       <c r="G20" t="n">
-        <v>1173</v>
+        <v>961</v>
       </c>
       <c r="H20" t="n">
-        <v>5774</v>
+        <v>4624</v>
       </c>
       <c r="I20" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1065,7 +1065,7 @@
         <v>4190988309</v>
       </c>
       <c r="D21" t="n">
-        <v>2977</v>
+        <v>5257</v>
       </c>
       <c r="E21" t="n">
         <v>610.08</v>
@@ -1074,10 +1074,10 @@
         <v>8141</v>
       </c>
       <c r="G21" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H21" t="n">
-        <v>4018</v>
+        <v>4000</v>
       </c>
       <c r="I21" t="n">
         <v>153</v>
@@ -1086,162 +1086,162 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>495403620</v>
       </c>
       <c r="C22" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D22" t="n">
-        <v>3070</v>
+        <v>5778</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>6379</v>
+        <v>1177</v>
       </c>
       <c r="G22" t="n">
-        <v>1010</v>
+        <v>1150</v>
       </c>
       <c r="H22" t="n">
-        <v>5030</v>
+        <v>5546</v>
       </c>
       <c r="I22" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C23" t="n">
-        <v>9811363528</v>
+        <v>2526158329</v>
       </c>
       <c r="D23" t="n">
-        <v>1296</v>
+        <v>1385</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
       </c>
       <c r="F23" t="n">
-        <v>6455</v>
+        <v>3408</v>
       </c>
       <c r="G23" t="n">
-        <v>1214</v>
+        <v>918</v>
       </c>
       <c r="H23" t="n">
-        <v>6063</v>
+        <v>4589</v>
       </c>
       <c r="I23" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C24" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D24" t="n">
-        <v>152</v>
+        <v>1607</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
       </c>
       <c r="F24" t="n">
-        <v>8141</v>
+        <v>1177</v>
       </c>
       <c r="G24" t="n">
-        <v>799</v>
+        <v>1150</v>
       </c>
       <c r="H24" t="n">
-        <v>4018</v>
+        <v>5546</v>
       </c>
       <c r="I24" t="n">
-        <v>153</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C25" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D25" t="n">
-        <v>4171</v>
+        <v>3714</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
       </c>
       <c r="F25" t="n">
-        <v>6379</v>
+        <v>6966</v>
       </c>
       <c r="G25" t="n">
-        <v>1010</v>
+        <v>961</v>
       </c>
       <c r="H25" t="n">
-        <v>5030</v>
+        <v>4624</v>
       </c>
       <c r="I25" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C26" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D26" t="n">
-        <v>3575</v>
+        <v>2584</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
       </c>
       <c r="F26" t="n">
-        <v>6455</v>
+        <v>6379</v>
       </c>
       <c r="G26" t="n">
-        <v>1214</v>
+        <v>934</v>
       </c>
       <c r="H26" t="n">
-        <v>6063</v>
+        <v>4305</v>
       </c>
       <c r="I26" t="n">
-        <v>246</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1260,112 +1260,112 @@
         <v>1177</v>
       </c>
       <c r="G27" t="n">
-        <v>1173</v>
+        <v>1150</v>
       </c>
       <c r="H27" t="n">
-        <v>5774</v>
+        <v>5546</v>
       </c>
       <c r="I27" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>63563817</v>
       </c>
       <c r="C28" t="n">
-        <v>4190988309</v>
+        <v>2526158329</v>
       </c>
       <c r="D28" t="n">
-        <v>5699</v>
+        <v>2052</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>8141</v>
+        <v>3408</v>
       </c>
       <c r="G28" t="n">
-        <v>799</v>
+        <v>918</v>
       </c>
       <c r="H28" t="n">
-        <v>4018</v>
+        <v>4589</v>
       </c>
       <c r="I28" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C29" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D29" t="n">
-        <v>6514</v>
+        <v>1203</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>6966</v>
+        <v>8141</v>
       </c>
       <c r="G29" t="n">
-        <v>914</v>
+        <v>798</v>
       </c>
       <c r="H29" t="n">
-        <v>4187</v>
+        <v>4000</v>
       </c>
       <c r="I29" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C30" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D30" t="n">
-        <v>1098</v>
+        <v>584</v>
       </c>
       <c r="E30" t="n">
         <v>610.08</v>
       </c>
       <c r="F30" t="n">
-        <v>8141</v>
+        <v>6966</v>
       </c>
       <c r="G30" t="n">
-        <v>799</v>
+        <v>961</v>
       </c>
       <c r="H30" t="n">
-        <v>4018</v>
+        <v>4624</v>
       </c>
       <c r="I30" t="n">
-        <v>153</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1375,7 +1375,7 @@
         <v>8878077181</v>
       </c>
       <c r="D31" t="n">
-        <v>1607</v>
+        <v>1048</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
@@ -1384,13 +1384,13 @@
         <v>1177</v>
       </c>
       <c r="G31" t="n">
-        <v>1173</v>
+        <v>1150</v>
       </c>
       <c r="H31" t="n">
-        <v>5774</v>
+        <v>5546</v>
       </c>
       <c r="I31" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32">
@@ -1400,65 +1400,65 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C32" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D32" t="n">
-        <v>609</v>
+        <v>4244</v>
       </c>
       <c r="E32" t="n">
         <v>610.08</v>
       </c>
       <c r="F32" t="n">
-        <v>6379</v>
+        <v>6966</v>
       </c>
       <c r="G32" t="n">
-        <v>1010</v>
+        <v>961</v>
       </c>
       <c r="H32" t="n">
-        <v>5030</v>
+        <v>4624</v>
       </c>
       <c r="I32" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C33" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D33" t="n">
-        <v>4593</v>
+        <v>5268</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>6966</v>
+        <v>8141</v>
       </c>
       <c r="G33" t="n">
-        <v>914</v>
+        <v>798</v>
       </c>
       <c r="H33" t="n">
-        <v>4187</v>
+        <v>4000</v>
       </c>
       <c r="I33" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1468,7 +1468,7 @@
         <v>2526158329</v>
       </c>
       <c r="D34" t="n">
-        <v>2397</v>
+        <v>6207</v>
       </c>
       <c r="E34" t="n">
         <v>610.08</v>
@@ -1477,10 +1477,10 @@
         <v>3408</v>
       </c>
       <c r="G34" t="n">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="H34" t="n">
-        <v>4528</v>
+        <v>4589</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1489,187 +1489,187 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C35" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D35" t="n">
-        <v>5219</v>
+        <v>2933</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>6455</v>
+        <v>6966</v>
       </c>
       <c r="G35" t="n">
-        <v>1214</v>
+        <v>961</v>
       </c>
       <c r="H35" t="n">
-        <v>6063</v>
+        <v>4624</v>
       </c>
       <c r="I35" t="n">
-        <v>246</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C36" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D36" t="n">
-        <v>1402</v>
+        <v>6390</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>6455</v>
+        <v>6966</v>
       </c>
       <c r="G36" t="n">
-        <v>1214</v>
+        <v>961</v>
       </c>
       <c r="H36" t="n">
-        <v>6063</v>
+        <v>4624</v>
       </c>
       <c r="I36" t="n">
-        <v>246</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C37" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D37" t="n">
-        <v>3989</v>
+        <v>2093</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
       </c>
       <c r="F37" t="n">
-        <v>1177</v>
+        <v>6379</v>
       </c>
       <c r="G37" t="n">
-        <v>1173</v>
+        <v>934</v>
       </c>
       <c r="H37" t="n">
-        <v>5774</v>
+        <v>4305</v>
       </c>
       <c r="I37" t="n">
-        <v>199</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>495403620</v>
       </c>
       <c r="C38" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D38" t="n">
-        <v>1048</v>
+        <v>2079</v>
       </c>
       <c r="E38" t="n">
         <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>1177</v>
+        <v>6379</v>
       </c>
       <c r="G38" t="n">
-        <v>1173</v>
+        <v>934</v>
       </c>
       <c r="H38" t="n">
-        <v>5774</v>
+        <v>4305</v>
       </c>
       <c r="I38" t="n">
-        <v>199</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C39" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D39" t="n">
-        <v>815</v>
+        <v>5257</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6966</v>
+        <v>8141</v>
       </c>
       <c r="G39" t="n">
-        <v>914</v>
+        <v>798</v>
       </c>
       <c r="H39" t="n">
-        <v>4187</v>
+        <v>4000</v>
       </c>
       <c r="I39" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C40" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D40" t="n">
-        <v>2195</v>
+        <v>6407</v>
       </c>
       <c r="E40" t="n">
         <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>6966</v>
+        <v>6455</v>
       </c>
       <c r="G40" t="n">
-        <v>914</v>
+        <v>1197</v>
       </c>
       <c r="H40" t="n">
-        <v>4187</v>
+        <v>5892</v>
       </c>
       <c r="I40" t="n">
-        <v>177</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result4_v2.xlsx
+++ b/results/excel/result4_v2.xlsx
@@ -466,63 +466,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C2" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D2" t="n">
-        <v>3202</v>
+        <v>5257</v>
       </c>
       <c r="E2" t="n">
         <v>610.08</v>
       </c>
       <c r="F2" t="n">
-        <v>6455</v>
+        <v>8141</v>
       </c>
       <c r="G2" t="n">
-        <v>1197</v>
+        <v>763</v>
       </c>
       <c r="H2" t="n">
-        <v>5892</v>
+        <v>3664</v>
       </c>
       <c r="I2" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C3" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D3" t="n">
-        <v>4340</v>
+        <v>5778</v>
       </c>
       <c r="E3" t="n">
         <v>610.08</v>
       </c>
       <c r="F3" t="n">
-        <v>6455</v>
+        <v>1177</v>
       </c>
       <c r="G3" t="n">
-        <v>1197</v>
+        <v>1112</v>
       </c>
       <c r="H3" t="n">
-        <v>5892</v>
+        <v>5185</v>
       </c>
       <c r="I3" t="n">
-        <v>242</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
@@ -532,59 +532,59 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C4" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D4" t="n">
-        <v>4870</v>
+        <v>3949</v>
       </c>
       <c r="E4" t="n">
         <v>610.08</v>
       </c>
       <c r="F4" t="n">
-        <v>6966</v>
+        <v>6379</v>
       </c>
       <c r="G4" t="n">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="H4" t="n">
-        <v>4624</v>
+        <v>4950</v>
       </c>
       <c r="I4" t="n">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C5" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D5" t="n">
-        <v>6083</v>
+        <v>1048</v>
       </c>
       <c r="E5" t="n">
         <v>610.08</v>
       </c>
       <c r="F5" t="n">
-        <v>8141</v>
+        <v>1177</v>
       </c>
       <c r="G5" t="n">
-        <v>798</v>
+        <v>1112</v>
       </c>
       <c r="H5" t="n">
-        <v>4000</v>
+        <v>5185</v>
       </c>
       <c r="I5" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -594,44 +594,44 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C6" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>3692</v>
       </c>
       <c r="E6" t="n">
         <v>610.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1177</v>
+        <v>6455</v>
       </c>
       <c r="G6" t="n">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="H6" t="n">
-        <v>5546</v>
+        <v>5481</v>
       </c>
       <c r="I6" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C7" t="n">
         <v>8878077181</v>
       </c>
       <c r="D7" t="n">
-        <v>1607</v>
+        <v>3989</v>
       </c>
       <c r="E7" t="n">
         <v>610.08</v>
@@ -640,137 +640,137 @@
         <v>1177</v>
       </c>
       <c r="G7" t="n">
-        <v>1150</v>
+        <v>1112</v>
       </c>
       <c r="H7" t="n">
-        <v>5546</v>
+        <v>5185</v>
       </c>
       <c r="I7" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>495403620</v>
       </c>
       <c r="C8" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D8" t="n">
-        <v>2742</v>
+        <v>3653</v>
       </c>
       <c r="E8" t="n">
         <v>610.08</v>
       </c>
       <c r="F8" t="n">
-        <v>6455</v>
+        <v>6379</v>
       </c>
       <c r="G8" t="n">
-        <v>1197</v>
+        <v>1002</v>
       </c>
       <c r="H8" t="n">
-        <v>5892</v>
+        <v>4950</v>
       </c>
       <c r="I8" t="n">
-        <v>242</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C9" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D9" t="n">
-        <v>4101</v>
+        <v>5288</v>
       </c>
       <c r="E9" t="n">
         <v>610.08</v>
       </c>
       <c r="F9" t="n">
-        <v>8141</v>
+        <v>6966</v>
       </c>
       <c r="G9" t="n">
-        <v>798</v>
+        <v>929</v>
       </c>
       <c r="H9" t="n">
-        <v>4000</v>
+        <v>4319</v>
       </c>
       <c r="I9" t="n">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>63563817</v>
       </c>
       <c r="C10" t="n">
-        <v>2526158329</v>
+        <v>1841014603</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>6086</v>
       </c>
       <c r="E10" t="n">
-        <v>304.94</v>
+        <v>610.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1704</v>
+        <v>2954</v>
       </c>
       <c r="G10" t="n">
-        <v>459</v>
+        <v>811</v>
       </c>
       <c r="H10" t="n">
-        <v>2294</v>
+        <v>4083</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C11" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D11" t="n">
-        <v>4017</v>
+        <v>5640</v>
       </c>
       <c r="E11" t="n">
         <v>610.08</v>
       </c>
       <c r="F11" t="n">
-        <v>8141</v>
+        <v>6455</v>
       </c>
       <c r="G11" t="n">
-        <v>798</v>
+        <v>1154</v>
       </c>
       <c r="H11" t="n">
-        <v>4000</v>
+        <v>5481</v>
       </c>
       <c r="I11" t="n">
-        <v>153</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
@@ -780,199 +780,199 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C12" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D12" t="n">
-        <v>4931</v>
+        <v>3882</v>
       </c>
       <c r="E12" t="n">
         <v>610.08</v>
       </c>
       <c r="F12" t="n">
-        <v>6379</v>
+        <v>6966</v>
       </c>
       <c r="G12" t="n">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="H12" t="n">
-        <v>4305</v>
+        <v>4319</v>
       </c>
       <c r="I12" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C13" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D13" t="n">
-        <v>1607</v>
+        <v>3305</v>
       </c>
       <c r="E13" t="n">
         <v>610.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1177</v>
+        <v>6966</v>
       </c>
       <c r="G13" t="n">
-        <v>1150</v>
+        <v>929</v>
       </c>
       <c r="H13" t="n">
-        <v>5546</v>
+        <v>4319</v>
       </c>
       <c r="I13" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C14" t="n">
-        <v>9628223555</v>
+        <v>1841014603</v>
       </c>
       <c r="D14" t="n">
-        <v>2795</v>
+        <v>3304</v>
       </c>
       <c r="E14" t="n">
         <v>610.08</v>
       </c>
       <c r="F14" t="n">
-        <v>6379</v>
+        <v>2954</v>
       </c>
       <c r="G14" t="n">
-        <v>934</v>
+        <v>811</v>
       </c>
       <c r="H14" t="n">
-        <v>4305</v>
+        <v>4083</v>
       </c>
       <c r="I14" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C15" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D15" t="n">
-        <v>3060</v>
+        <v>3420</v>
       </c>
       <c r="E15" t="n">
         <v>610.08</v>
       </c>
       <c r="F15" t="n">
-        <v>6379</v>
+        <v>6966</v>
       </c>
       <c r="G15" t="n">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="H15" t="n">
-        <v>4305</v>
+        <v>4319</v>
       </c>
       <c r="I15" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C16" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D16" t="n">
-        <v>2233</v>
+        <v>2083</v>
       </c>
       <c r="E16" t="n">
         <v>610.08</v>
       </c>
       <c r="F16" t="n">
-        <v>6455</v>
+        <v>2954</v>
       </c>
       <c r="G16" t="n">
-        <v>1197</v>
+        <v>811</v>
       </c>
       <c r="H16" t="n">
-        <v>5892</v>
+        <v>4083</v>
       </c>
       <c r="I16" t="n">
-        <v>242</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C17" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D17" t="n">
-        <v>5497</v>
+        <v>5176</v>
       </c>
       <c r="E17" t="n">
         <v>610.08</v>
       </c>
       <c r="F17" t="n">
-        <v>6455</v>
+        <v>2954</v>
       </c>
       <c r="G17" t="n">
-        <v>1197</v>
+        <v>811</v>
       </c>
       <c r="H17" t="n">
-        <v>5892</v>
+        <v>4083</v>
       </c>
       <c r="I17" t="n">
-        <v>242</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C18" t="n">
         <v>9628223555</v>
       </c>
       <c r="D18" t="n">
-        <v>5779</v>
+        <v>2441</v>
       </c>
       <c r="E18" t="n">
         <v>610.08</v>
@@ -981,137 +981,137 @@
         <v>6379</v>
       </c>
       <c r="G18" t="n">
-        <v>934</v>
+        <v>1002</v>
       </c>
       <c r="H18" t="n">
-        <v>4305</v>
+        <v>4950</v>
       </c>
       <c r="I18" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C19" t="n">
-        <v>9811363528</v>
+        <v>9628223555</v>
       </c>
       <c r="D19" t="n">
-        <v>2859</v>
+        <v>5721</v>
       </c>
       <c r="E19" t="n">
         <v>610.08</v>
       </c>
       <c r="F19" t="n">
-        <v>6455</v>
+        <v>6379</v>
       </c>
       <c r="G19" t="n">
-        <v>1197</v>
+        <v>1002</v>
       </c>
       <c r="H19" t="n">
-        <v>5892</v>
+        <v>4950</v>
       </c>
       <c r="I19" t="n">
-        <v>242</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C20" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D20" t="n">
-        <v>6256</v>
+        <v>5778</v>
       </c>
       <c r="E20" t="n">
         <v>610.08</v>
       </c>
       <c r="F20" t="n">
-        <v>6966</v>
+        <v>1177</v>
       </c>
       <c r="G20" t="n">
-        <v>961</v>
+        <v>1112</v>
       </c>
       <c r="H20" t="n">
-        <v>4624</v>
+        <v>5185</v>
       </c>
       <c r="I20" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C21" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D21" t="n">
-        <v>5257</v>
+        <v>6210</v>
       </c>
       <c r="E21" t="n">
         <v>610.08</v>
       </c>
       <c r="F21" t="n">
-        <v>8141</v>
+        <v>6379</v>
       </c>
       <c r="G21" t="n">
-        <v>798</v>
+        <v>1002</v>
       </c>
       <c r="H21" t="n">
-        <v>4000</v>
+        <v>4950</v>
       </c>
       <c r="I21" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C22" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D22" t="n">
-        <v>5778</v>
+        <v>3076</v>
       </c>
       <c r="E22" t="n">
         <v>610.08</v>
       </c>
       <c r="F22" t="n">
-        <v>1177</v>
+        <v>6455</v>
       </c>
       <c r="G22" t="n">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="H22" t="n">
-        <v>5546</v>
+        <v>5481</v>
       </c>
       <c r="I22" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
@@ -1121,75 +1121,75 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C23" t="n">
-        <v>2526158329</v>
+        <v>8878077181</v>
       </c>
       <c r="D23" t="n">
-        <v>1385</v>
+        <v>1048</v>
       </c>
       <c r="E23" t="n">
         <v>610.08</v>
       </c>
       <c r="F23" t="n">
-        <v>3408</v>
+        <v>1177</v>
       </c>
       <c r="G23" t="n">
-        <v>918</v>
+        <v>1112</v>
       </c>
       <c r="H23" t="n">
-        <v>4589</v>
+        <v>5185</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C24" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D24" t="n">
-        <v>1607</v>
+        <v>3597</v>
       </c>
       <c r="E24" t="n">
         <v>610.08</v>
       </c>
       <c r="F24" t="n">
-        <v>1177</v>
+        <v>6455</v>
       </c>
       <c r="G24" t="n">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="H24" t="n">
-        <v>5546</v>
+        <v>5481</v>
       </c>
       <c r="I24" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C25" t="n">
         <v>9630806627</v>
       </c>
       <c r="D25" t="n">
-        <v>3714</v>
+        <v>1575</v>
       </c>
       <c r="E25" t="n">
         <v>610.08</v>
@@ -1198,19 +1198,19 @@
         <v>6966</v>
       </c>
       <c r="G25" t="n">
-        <v>961</v>
+        <v>929</v>
       </c>
       <c r="H25" t="n">
-        <v>4624</v>
+        <v>4319</v>
       </c>
       <c r="I25" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1220,7 +1220,7 @@
         <v>9628223555</v>
       </c>
       <c r="D26" t="n">
-        <v>2584</v>
+        <v>1683</v>
       </c>
       <c r="E26" t="n">
         <v>610.08</v>
@@ -1229,44 +1229,44 @@
         <v>6379</v>
       </c>
       <c r="G26" t="n">
-        <v>934</v>
+        <v>1002</v>
       </c>
       <c r="H26" t="n">
-        <v>4305</v>
+        <v>4950</v>
       </c>
       <c r="I26" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>525368335</v>
       </c>
       <c r="C27" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D27" t="n">
-        <v>3989</v>
+        <v>733</v>
       </c>
       <c r="E27" t="n">
         <v>610.08</v>
       </c>
       <c r="F27" t="n">
-        <v>1177</v>
+        <v>6455</v>
       </c>
       <c r="G27" t="n">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="H27" t="n">
-        <v>5546</v>
+        <v>5481</v>
       </c>
       <c r="I27" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28">
@@ -1279,124 +1279,124 @@
         <v>63563817</v>
       </c>
       <c r="C28" t="n">
-        <v>2526158329</v>
+        <v>1841014603</v>
       </c>
       <c r="D28" t="n">
-        <v>2052</v>
+        <v>800</v>
       </c>
       <c r="E28" t="n">
         <v>610.08</v>
       </c>
       <c r="F28" t="n">
-        <v>3408</v>
+        <v>2954</v>
       </c>
       <c r="G28" t="n">
-        <v>918</v>
+        <v>811</v>
       </c>
       <c r="H28" t="n">
-        <v>4589</v>
+        <v>4083</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C29" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D29" t="n">
-        <v>1203</v>
+        <v>3989</v>
       </c>
       <c r="E29" t="n">
         <v>610.08</v>
       </c>
       <c r="F29" t="n">
-        <v>8141</v>
+        <v>1177</v>
       </c>
       <c r="G29" t="n">
-        <v>798</v>
+        <v>1112</v>
       </c>
       <c r="H29" t="n">
-        <v>4000</v>
+        <v>5185</v>
       </c>
       <c r="I29" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C30" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D30" t="n">
-        <v>584</v>
+        <v>5374</v>
       </c>
       <c r="E30" t="n">
-        <v>610.08</v>
+        <v>304.94</v>
       </c>
       <c r="F30" t="n">
-        <v>6966</v>
+        <v>4069</v>
       </c>
       <c r="G30" t="n">
-        <v>961</v>
+        <v>382</v>
       </c>
       <c r="H30" t="n">
-        <v>4624</v>
+        <v>1831</v>
       </c>
       <c r="I30" t="n">
-        <v>186</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C31" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D31" t="n">
-        <v>1048</v>
+        <v>152</v>
       </c>
       <c r="E31" t="n">
         <v>610.08</v>
       </c>
       <c r="F31" t="n">
-        <v>1177</v>
+        <v>8141</v>
       </c>
       <c r="G31" t="n">
-        <v>1150</v>
+        <v>763</v>
       </c>
       <c r="H31" t="n">
-        <v>5546</v>
+        <v>3664</v>
       </c>
       <c r="I31" t="n">
-        <v>195</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1406,7 +1406,7 @@
         <v>9630806627</v>
       </c>
       <c r="D32" t="n">
-        <v>4244</v>
+        <v>6578</v>
       </c>
       <c r="E32" t="n">
         <v>610.08</v>
@@ -1415,13 +1415,13 @@
         <v>6966</v>
       </c>
       <c r="G32" t="n">
-        <v>961</v>
+        <v>929</v>
       </c>
       <c r="H32" t="n">
-        <v>4624</v>
+        <v>4319</v>
       </c>
       <c r="I32" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
@@ -1431,41 +1431,41 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C33" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D33" t="n">
-        <v>5268</v>
+        <v>3989</v>
       </c>
       <c r="E33" t="n">
         <v>610.08</v>
       </c>
       <c r="F33" t="n">
-        <v>8141</v>
+        <v>1177</v>
       </c>
       <c r="G33" t="n">
-        <v>798</v>
+        <v>1112</v>
       </c>
       <c r="H33" t="n">
-        <v>4000</v>
+        <v>5185</v>
       </c>
       <c r="I33" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>63563817</v>
       </c>
       <c r="C34" t="n">
-        <v>2526158329</v>
+        <v>4190988309</v>
       </c>
       <c r="D34" t="n">
         <v>6207</v>
@@ -1474,94 +1474,94 @@
         <v>610.08</v>
       </c>
       <c r="F34" t="n">
-        <v>3408</v>
+        <v>8141</v>
       </c>
       <c r="G34" t="n">
-        <v>918</v>
+        <v>763</v>
       </c>
       <c r="H34" t="n">
-        <v>4589</v>
+        <v>3664</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C35" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D35" t="n">
-        <v>2933</v>
+        <v>5849</v>
       </c>
       <c r="E35" t="n">
         <v>610.08</v>
       </c>
       <c r="F35" t="n">
-        <v>6966</v>
+        <v>2954</v>
       </c>
       <c r="G35" t="n">
-        <v>961</v>
+        <v>811</v>
       </c>
       <c r="H35" t="n">
-        <v>4624</v>
+        <v>4083</v>
       </c>
       <c r="I35" t="n">
-        <v>186</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C36" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D36" t="n">
-        <v>6390</v>
+        <v>2826</v>
       </c>
       <c r="E36" t="n">
         <v>610.08</v>
       </c>
       <c r="F36" t="n">
-        <v>6966</v>
+        <v>6455</v>
       </c>
       <c r="G36" t="n">
-        <v>961</v>
+        <v>1154</v>
       </c>
       <c r="H36" t="n">
-        <v>4624</v>
+        <v>5481</v>
       </c>
       <c r="I36" t="n">
-        <v>186</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C37" t="n">
         <v>9628223555</v>
       </c>
       <c r="D37" t="n">
-        <v>2093</v>
+        <v>646</v>
       </c>
       <c r="E37" t="n">
         <v>610.08</v>
@@ -1570,13 +1570,13 @@
         <v>6379</v>
       </c>
       <c r="G37" t="n">
-        <v>934</v>
+        <v>1002</v>
       </c>
       <c r="H37" t="n">
-        <v>4305</v>
+        <v>4950</v>
       </c>
       <c r="I37" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38">
@@ -1586,28 +1586,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C38" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D38" t="n">
-        <v>2079</v>
+        <v>2226</v>
       </c>
       <c r="E38" t="n">
         <v>610.08</v>
       </c>
       <c r="F38" t="n">
-        <v>6379</v>
+        <v>6455</v>
       </c>
       <c r="G38" t="n">
-        <v>934</v>
+        <v>1154</v>
       </c>
       <c r="H38" t="n">
-        <v>4305</v>
+        <v>5481</v>
       </c>
       <c r="I38" t="n">
-        <v>152</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39">
@@ -1617,59 +1617,59 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C39" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D39" t="n">
-        <v>5257</v>
+        <v>308</v>
       </c>
       <c r="E39" t="n">
         <v>610.08</v>
       </c>
       <c r="F39" t="n">
-        <v>8141</v>
+        <v>6966</v>
       </c>
       <c r="G39" t="n">
-        <v>798</v>
+        <v>929</v>
       </c>
       <c r="H39" t="n">
-        <v>4000</v>
+        <v>4319</v>
       </c>
       <c r="I39" t="n">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C40" t="n">
-        <v>9811363528</v>
+        <v>1841014603</v>
       </c>
       <c r="D40" t="n">
-        <v>6407</v>
+        <v>5010</v>
       </c>
       <c r="E40" t="n">
         <v>610.08</v>
       </c>
       <c r="F40" t="n">
-        <v>6455</v>
+        <v>2954</v>
       </c>
       <c r="G40" t="n">
-        <v>1197</v>
+        <v>811</v>
       </c>
       <c r="H40" t="n">
-        <v>5892</v>
+        <v>4083</v>
       </c>
       <c r="I40" t="n">
-        <v>242</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
